--- a/data/daily/2026-10/2026-10-23.xlsx
+++ b/data/daily/2026-10/2026-10-23.xlsx
@@ -11,7 +11,9 @@
     <sheet name="카카오선물하기_카드형" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="다이소몰" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="다이소몰_카드형" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="카테고리통계" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="올리브영" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="올리브영_카드형" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="카테고리통계" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1168,14 +1170,64 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1190,17 +1242,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1215,17 +1267,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1240,17 +1317,67 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1265,135 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1423,9 +1425,264 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -1443,12 +1700,267 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>3</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1473,7 +1985,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1498,7 +2010,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1523,7 +2035,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1548,7 +2060,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1598,7 +2110,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1623,7 +2135,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1648,7 +2160,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2086,9 +2598,21 @@
       <c r="J2" t="n">
         <v>16335</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>선물용으로 높은 만족도 — 생일이나 특별한 날 감사 선물로 주고받기 좋음</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>피로 회복 및 컨디션 개선 — 섭취 시 피로감이 줄고 컨디션이 나아지는 느낌을 받음</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>섭취하기 편리한 알약과 맛 — 알약 크기가 작고 맛도 거부감이 없어 먹기 편함</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -2133,9 +2657,21 @@
       <c r="J3" t="n">
         <v>15675</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>피로 회복과 기력 증진 — 피로할 때나 기력이 떨어질 때 도움이 됨</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>휴대와 섭취의 간편함 — 포장이 깔끔하여 휴대성이 좋고 간편하게 먹기 용이함</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>빠른 배송 서비스 — 주문 후 배송이 빠르게 완료됨</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -2180,9 +2716,21 @@
       <c r="J4" t="n">
         <v>3422</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>선물용으로 좋은 고급스러움 — 비주얼이 고급스럽고 넉넉한 수량으로 선물하기 좋음</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>활력 증진 및 진한 액상 — 다른 제품에 비해 액상 농도가 진하고 지칠 때 힘이 남</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>편리한 휴대성과 실용성 — 하나씩 간편하게 챙겨 먹기 유용함</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -2227,11 +2775,27 @@
       <c r="J5" t="n">
         <v>6532</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>맛있는 젤리 제형 — 과일맛이 나고 적당히 달고 쫄깃하여 간식처럼 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>물 없이 먹는 간편함 — 바쁜 아침에도 물 없이 씹어서 간편하게 섭취함</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>개봉하기 어려운 포장 — 제품 포장이 잘 뜯어지지 않아 개봉 시 불편함</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>약처럼 느껴지지 않는 제형 — 하리보 젤리 같아서 성인용 영양제 느낌이 적음</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
@@ -2274,9 +2838,21 @@
       <c r="J6" t="n">
         <v>832</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>선물용으로 우수한 만족도 — 환절기나 지인 선물로 주고받기 좋음</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>피로 회복 도움 — 일상의 피로 회복과 활력 충전에 도움이 됨</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>섭취 및 휴대 편의성 — 먹기 편하고 휴대하기 용이한 포장 형태임</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2321,10 +2897,26 @@
       <c r="J7" t="n">
         <v>1799</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>상큼 달콤한 맛과 빠른 배송 — 신맛이 적고 망고맛 등 달콤한 맛이 나며 배송이 빠름</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>컨디션 회복과 활력 증진 — 섭취 후 기운이 나고 컨디션이 좋아지는 효과를 느낌</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>버튼을 섞는 재미 — 버튼을 눌러 분말과 액상을 섞어 마시는 방식이 흥미로움</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>개봉 및 버튼 조작 불편함 — 버튼이 뻑뻑하고 비닐 포장이 잘 벗겨지지 않아 개봉이 불편함</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -2366,11 +2958,23 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>8762</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+        <v>8763</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>간편한 액상 제형 — 마시는 액상 형태로 언제 어디서나 간편하게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>빠른 배송 서비스 — 배송이 빠르게 도착하여 만족스러움</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>피로 회복 및 건강 증진 — 피곤할 때 섭취하면 기운이 나고 건강 관리에 도움 됨</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -2413,12 +3017,28 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>980</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+        <v>981</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>믿을 수 있는 품질과 브랜드 — 영국산 원료 사용 및 검증된 브랜드로 신뢰감이 높음</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>고함량 비타민C 효과 — 고용량 메가도스 용량으로 피로 회복에 효과적임</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>빠른 배송 및 가성비 — 행사 할인가로 저렴하고 배송이 빠름</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>매우 강한 신맛 — 신맛이 강하여 물과 함께 섭취해야 함</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -2462,10 +3082,22 @@
       <c r="J10" t="n">
         <v>788</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>확실한 피로 회복 효과 — 바쁜 일상이나 피로할 때 활력을 더해주는 효과가 뛰어남</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>편리한 섭취 방식 — 포장이 잘 되어 있고 먹기가 간편함</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>감기약 같은 아쉬운 맛 — 오렌지맛 감기약 느낌이 나 맛에 대한 만족도는 떨어짐</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -2509,9 +3141,21 @@
       <c r="J11" t="n">
         <v>844</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>위생적이고 편리한 이중 구조 — 액상과 알약이 구분되어 있어 위생적이고 섭취가 편리함</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>빠른 피로 회복 효과 — 섭취 시 피로가 줄고 하루 종일 에너지가 유지됨</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>빠른 배송과 꼼꼼한 포장 — 포장 상태가 좋고 배송이 신속하게 진행됨</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -2554,12 +3198,28 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>30</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>다양한 맛과 부드러운 식감 — 맛 종류가 다양하여 질리지 않고 고기가 부드러움</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>간편한 조리 방식 — 전자레인지에 간단히 데워 식단으로 먹기 편리함</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>신속한 고객 응대 — 누락 건에 대한 문의 시 즉각적으로 빠르게 재배송함</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>부분적인 가열의 필요성 — 통살 제품은 충분히 데워야 속까지 잘 익음</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
@@ -2603,10 +3263,26 @@
       <c r="J13" t="n">
         <v>1763</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>고소하고 맛있는 풍미 — 미숫가루처럼 꼬수운 맛이 나 먹기 부담이 없음</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>소화 촉진 및 편안한 속 — 식후 더부룩함이 줄어들고 속이 편안해짐</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>푸짐한 증정품과 고급 포장 — 견과류바 등 사은품 구성이 좋고 선물용 포장이 고급스러움</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>이벤트 기프티콘 확인 불편 — 증정 기프티콘의 수령 위치나 확인 방법 안내가 모호함</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -2650,10 +3326,22 @@
       <c r="J14" t="n">
         <v>947</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>달콤하고 편안한 섭취 — 맛이 달콤하여 부담 없이 챙겨 먹기 용이함</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>풍성한 사은품 혜택 — 견과류바와 단백칩 등 다채로운 증정품을 함께 제공함</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>아쉬운 맛과 향 — 기존 프리미엄 제품에 비해 특유의 향과 맛에 거부감이 있음</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
@@ -2697,17 +3385,33 @@
       <c r="J15" t="n">
         <v>161</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>뛰어난 맛과 포만감 — 떡볶이맛 등 양념이 맛있고 한 개만 먹어도 든든함</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>빠른 배송 및 사은품 제공 — 발송이 빠르고 활용도 높은 보냉백 사은품을 증정함</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>강한 양념 간 — 단독으로 먹기에 간이 다소 세게 느껴짐</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>구성 대비 아쉬운 가격 — 저렴한 제품 위주의 구성 대비 가격이 비싸게 느껴짐</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2715,46 +3419,62 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
+          <t>단백이 계란흰자 에그 프로틴 40개입(달걀 단백질 간편식)+(증정)단백이 구운맛 2개</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>가농</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/14380726</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261021165641_99634da9bf9f4b3d8e560929369229b1.png</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>278</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>비린 맛 없는 계란 흰자 — 계란 특유의 비린내가 없고 퍽퍽하지 않아 섭취하기 좋음</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>편리한 섭취와 높은 포만감 — 껍질을 깔 필요 없이 언제 어디서나 간편하게 먹고 포만감이 높음</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>낮은 칼로리와 뛰어난 영양 — 칼로리 부담 없이 단백질을 효율적으로 보충 가능함</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>아쉬운 외관 포장 상태 — 택배 박스 외관이 지저분하거나 재활용한 느낌을 줌</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2762,37 +3482,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>단백이 계란흰자 99.5% 에그 프로틴 40개입(달걀 단백질 간편식)+(증정)단백이 구운맛 2개</t>
+          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>가농</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14380726</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261021165641_99634da9bf9f4b3d8e560929369229b1.png</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>30</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+        <v>278</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>다양하고 맛있는 풍미 — 쿠키앤크림, 소다아이스크림 등 디저트 같은 맛으로 맛있음</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>알찬 굿즈와 증정품 구성 — 포토카드 및 단백질바 등 알찬 구성품이 제공됨</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -2838,9 +3566,21 @@
       <c r="J18" t="n">
         <v>70</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>촉촉한 식감과 맛있는 양념 — 닭가슴살이 퍽퍽하지 않고 촉촉하며 소스 맛이 훌륭함</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>간편한 조리법 — 전자레인지에 간편하게 데워 바로 먹기 편리함</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>빠르고 안전한 배송 — 배송이 빠르고 포장이 튼튼하게 유지되어 전달됨</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -2856,38 +3596,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월(+선물포장)+쇼핑백+그린캡슐레이션효소 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>64,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13255641</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261022082137_8413f613a8ac4edb9b69847f419517ca.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>33</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+        <v>109</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 머리 아픔이나 숙취가 크게 줄어듦</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>맛있고 간편한 액상 스틱 — 달콤한 맛으로 거부감이 없고 물 없이 마시는 스틱 형태라 편리함</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>우수한 휴대성과 구성 — 개별 포장으로 술자리에 휴대하기 용이함</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -2903,38 +3655,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월(+선물포장)+쇼핑백+그린캡슐레이션효소 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>64,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/13255641</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261022082137_8413f613a8ac4edb9b69847f419517ca.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>109</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>맛있는 고구마맛 분말 — 달콤한 고구마맛에 입자가 고와 목에 걸리지 않고 맛있음</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>빠른 소화 및 속 편함 — 식후 더부룩할 때 먹으면 금방 소화되어 속이 편안해짐</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>고급 포장과 신속한 배송 — 쇼핑백이 동봉된 고급스러운 포장에 배송이 신속함</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -2979,9 +3743,21 @@
       <c r="J21" t="n">
         <v>760</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>고급스러운 선물 패키지 — 선물 포장과 구성품이 매우 고급스럽고 예뻐 선물용으로 뛰어남</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>맛있고 간편한 앰플 제형 — 하루 한 병씩 맛있게 섭취할 수 있어 간편함</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>피부 수분과 탄력 기대 — 꾸준히 섭취 시 피부가 촉촉해지고 피로감이 줄어듦</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -3322,10 +4098,10 @@
         <v>1799</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8762</v>
+        <v>8763</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>788</v>
@@ -3334,24 +4110,82 @@
         <v>844</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>선물용으로 높은 만족도 — 생일이나 특별한 날 감사 선물로 주고받기 좋음
+피로 회복 및 컨디션 개선 — 섭취 시 피로감이 줄고 컨디션이 나아지는 느낌을 받음
+섭취하기 편리한 알약과 맛 — 알약 크기가 작고 맛도 거부감이 없어 먹기 편함</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>피로 회복과 기력 증진 — 피로할 때나 기력이 떨어질 때 도움이 됨
+휴대와 섭취의 간편함 — 포장이 깔끔하여 휴대성이 좋고 간편하게 먹기 용이함
+빠른 배송 서비스 — 주문 후 배송이 빠르게 완료됨</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>선물용으로 좋은 고급스러움 — 비주얼이 고급스럽고 넉넉한 수량으로 선물하기 좋음
+활력 증진 및 진한 액상 — 다른 제품에 비해 액상 농도가 진하고 지칠 때 힘이 남
+편리한 휴대성과 실용성 — 하나씩 간편하게 챙겨 먹기 유용함</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>맛있는 젤리 제형 — 과일맛이 나고 적당히 달고 쫄깃하여 간식처럼 섭취 가능함
+물 없이 먹는 간편함 — 바쁜 아침에도 물 없이 씹어서 간편하게 섭취함</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>선물용으로 우수한 만족도 — 환절기나 지인 선물로 주고받기 좋음
+피로 회복 도움 — 일상의 피로 회복과 활력 충전에 도움이 됨
+섭취 및 휴대 편의성 — 먹기 편하고 휴대하기 용이한 포장 형태임</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>상큼 달콤한 맛과 빠른 배송 — 신맛이 적고 망고맛 등 달콤한 맛이 나며 배송이 빠름
+컨디션 회복과 활력 증진 — 섭취 후 기운이 나고 컨디션이 좋아지는 효과를 느낌
+버튼을 섞는 재미 — 버튼을 눌러 분말과 액상을 섞어 마시는 방식이 흥미로움</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>간편한 액상 제형 — 마시는 액상 형태로 언제 어디서나 간편하게 섭취 가능함
+빠른 배송 서비스 — 배송이 빠르게 도착하여 만족스러움
+피로 회복 및 건강 증진 — 피곤할 때 섭취하면 기운이 나고 건강 관리에 도움 됨</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>믿을 수 있는 품질과 브랜드 — 영국산 원료 사용 및 검증된 브랜드로 신뢰감이 높음
+고함량 비타민C 효과 — 고용량 메가도스 용량으로 피로 회복에 효과적임
+빠른 배송 및 가성비 — 행사 할인가로 저렴하고 배송이 빠름</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>확실한 피로 회복 효과 — 바쁜 일상이나 피로할 때 활력을 더해주는 효과가 뛰어남
+편리한 섭취 방식 — 포장이 잘 되어 있고 먹기가 간편함</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>위생적이고 편리한 이중 구조 — 액상과 알약이 구분되어 있어 위생적이고 섭취가 편리함
+빠른 피로 회복 효과 — 섭취 시 피로가 줄고 하루 종일 에너지가 유지됨
+빠른 배송과 꼼꼼한 포장 — 포장 상태가 좋고 배송이 신속하게 진행됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -3360,12 +4194,29 @@
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>개봉하기 어려운 포장 — 제품 포장이 잘 뜯어지지 않아 개봉 시 불편함
+약처럼 느껴지지 않는 제형 — 하리보 젤리 같아서 성인용 영양제 느낌이 적음</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>개봉 및 버튼 조작 불편함 — 버튼이 뻑뻑하고 비닐 포장이 잘 벗겨지지 않아 개봉이 불편함</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>매우 강한 신맛 — 신맛이 강하여 물과 함께 섭취해야 함</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>감기약 같은 아쉬운 맛 — 오렌지맛 감기약 느낌이 나 맛에 대한 만족도는 떨어짐</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -3584,12 +4435,12 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -3641,14 +4492,14 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
+          <t>가농</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>가농</t>
-        </is>
-      </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
@@ -3656,12 +4507,12 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -3698,14 +4549,14 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
+          <t>단백이 계란흰자 에그 프로틴 40개입(달걀 단백질 간편식)+(증정)단백이 구운맛 2개</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
           <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>단백이 계란흰자 99.5% 에그 프로틴 40개입(달걀 단백질 간편식)+(증정)단백이 구운맛 2개</t>
-        </is>
-      </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
           <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
@@ -3713,12 +4564,12 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 파로효소 캡슐레이션 3개월(+선물포장)+쇼핑백+그린캡슐레이션효소 증정</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -3771,7 +4622,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>1763</v>
@@ -3783,52 +4634,130 @@
         <v>161</v>
       </c>
       <c r="G19" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>278</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>30</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>70</v>
       </c>
       <c r="J19" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="K19" s="3" t="n">
         <v>33</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>109</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>760</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="90" customHeight="1">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>다양한 맛과 부드러운 식감 — 맛 종류가 다양하여 질리지 않고 고기가 부드러움
+간편한 조리 방식 — 전자레인지에 간단히 데워 식단으로 먹기 편리함
+신속한 고객 응대 — 누락 건에 대한 문의 시 즉각적으로 빠르게 재배송함</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>고소하고 맛있는 풍미 — 미숫가루처럼 꼬수운 맛이 나 먹기 부담이 없음
+소화 촉진 및 편안한 속 — 식후 더부룩함이 줄어들고 속이 편안해짐
+푸짐한 증정품과 고급 포장 — 견과류바 등 사은품 구성이 좋고 선물용 포장이 고급스러움</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>달콤하고 편안한 섭취 — 맛이 달콤하여 부담 없이 챙겨 먹기 용이함
+풍성한 사은품 혜택 — 견과류바와 단백칩 등 다채로운 증정품을 함께 제공함</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>뛰어난 맛과 포만감 — 떡볶이맛 등 양념이 맛있고 한 개만 먹어도 든든함
+빠른 배송 및 사은품 제공 — 발송이 빠르고 활용도 높은 보냉백 사은품을 증정함</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>비린 맛 없는 계란 흰자 — 계란 특유의 비린내가 없고 퍽퍽하지 않아 섭취하기 좋음
+편리한 섭취와 높은 포만감 — 껍질을 깔 필요 없이 언제 어디서나 간편하게 먹고 포만감이 높음
+낮은 칼로리와 뛰어난 영양 — 칼로리 부담 없이 단백질을 효율적으로 보충 가능함</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>다양하고 맛있는 풍미 — 쿠키앤크림, 소다아이스크림 등 디저트 같은 맛으로 맛있음
+알찬 굿즈와 증정품 구성 — 포토카드 및 단백질바 등 알찬 구성품이 제공됨</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>촉촉한 식감과 맛있는 양념 — 닭가슴살이 퍽퍽하지 않고 촉촉하며 소스 맛이 훌륭함
+간편한 조리법 — 전자레인지에 간편하게 데워 바로 먹기 편리함
+빠르고 안전한 배송 — 배송이 빠르고 포장이 튼튼하게 유지되어 전달됨</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 머리 아픔이나 숙취가 크게 줄어듦
+맛있고 간편한 액상 스틱 — 달콤한 맛으로 거부감이 없고 물 없이 마시는 스틱 형태라 편리함
+우수한 휴대성과 구성 — 개별 포장으로 술자리에 휴대하기 용이함</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>맛있는 고구마맛 분말 — 달콤한 고구마맛에 입자가 고와 목에 걸리지 않고 맛있음
+빠른 소화 및 속 편함 — 식후 더부룩할 때 먹으면 금방 소화되어 속이 편안해짐
+고급 포장과 신속한 배송 — 쇼핑백이 동봉된 고급스러운 포장에 배송이 신속함</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>고급스러운 선물 패키지 — 선물 포장과 구성품이 매우 고급스럽고 예뻐 선물용으로 뛰어남
+맛있고 간편한 앰플 제형 — 하루 한 병씩 맛있게 섭취할 수 있어 간편함
+피부 수분과 탄력 기대 — 꾸준히 섭취 시 피부가 촉촉해지고 피로감이 줄어듦</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>부분적인 가열의 필요성 — 통살 제품은 충분히 데워야 속까지 잘 익음</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>이벤트 기프티콘 확인 불편 — 증정 기프티콘의 수령 위치나 확인 방법 안내가 모호함</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>아쉬운 맛과 향 — 기존 프리미엄 제품에 비해 특유의 향과 맛에 거부감이 있음</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>강한 양념 간 — 단독으로 먹기에 간이 다소 세게 느껴짐
+구성 대비 아쉬운 가격 — 저렴한 제품 위주의 구성 대비 가격이 비싸게 느껴짐</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>아쉬운 외관 포장 상태 — 택배 박스 외관이 지저분하거나 재활용한 느낌을 줌</t>
+        </is>
+      </c>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
@@ -3863,27 +4792,27 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
           <t>26,900원</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>33,000원</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>33,200원</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>33,000원</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>64,900원</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>33,200원</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -4078,7 +5007,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4086,37 +5015,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>904</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+        <v>7563</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 합리적인 가격으로 부담 없이 구매 가능함</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>피로 감소 체감 — 섭취 후 확실히 피로감이 줄어드는 느낌을 받음</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -4125,7 +5062,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4133,12 +5070,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4148,24 +5085,36 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581101&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260601/nkEyZw9TcKRMHbTvSy6D591581101_00_00nkEyZw9TcKRMHbTvSy6D.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>904</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+        <v>6868</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>저렴한 가격과 접근성 — 착한 가격에 부담 없이 구매하여 섭취할 수 있음</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>입문용으로 적합 — 오메가3를 처음 접하는 입문자에게 적합함</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>미미한 효능 체감 — 단기 섭취 시 명확한 효과를 체감하기 어려움</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -4180,12 +5129,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] [인교진 PICK] 스트레스 케어 올인원 15포 15일분</t>
+          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4195,23 +5144,35 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991022&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627034&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260928/lj0OQ0BySSR6nkU7Tv8A033991022_00_00lj0OQ0BySSR6nkU7Tv8A.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260810/jotmVom4KndGXbIlPcuj032627034_00_01jotmVom4KndGXbIlPcuj.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>124</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+        <v>1188</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>상큼한 레몬 맛과 가성비 — 가격이 저렴하고 상큼하여 부담 없이 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>공복 섭취의 간편함 — 아침 공복에 마시기 편리한 포장 구조임</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>신속한 배송 — 배송이 빠르게 처리되어 받아볼 수 있음</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -4219,7 +5180,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4227,12 +5188,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CJ 카무트 곡물과채콤부 화사 효소 10포 10일분</t>
+          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CJ웰케어</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4242,23 +5203,35 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=139213437&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580541&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/2v2CuiCUbhEwDNpboF5B139213437_00_002v2CuiCUbhEwDNpboF5B.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250430/yuK2zGjcuX8RmMDP9k9P591580541_00_00yuK2zGjcuX8RmMDP9k9P.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1304</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>1888</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>작은 알약 크기와 목넘김 — 알약 크기가 작아 섭취 시 목넘김이 수월함</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>편리한 케이스 포장 — 가위 없이 쉽게 뜯어지도록 설계된 케이스가 편리함</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>높은 가성비 — 가격 대비 만족스러운 품질을 제공함</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -4266,7 +5239,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4274,7 +5247,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>대웅제약 콘드로이친 30정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4289,22 +5262,30 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000152&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/b7btdcjQN0UwyzjBmHvY600000152_00_00b7btdcjQN0UwyzjBmHvY.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2970</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+        <v>1310</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>저렴한 가격과 가성비 — 가격이 매우 싸서 부담 없이 시도해보기 좋음</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>빠른 배송 서비스 — 주문 후 배송이 빠름</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -4313,7 +5294,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4321,37 +5302,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306201&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/NBw0phjtTvR7tEfBicGr032306201_00_01NBw0phjtTvR7tEfBicGr.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.7</v>
       </c>
       <c r="J7" t="n">
-        <v>231</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+        <v>1561</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>우수한 가성비 — 타 다이어트 보조제 대비 가격이 매우 저렴함</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>식후 마음의 안정 — 식사 후 복용 시 심리적으로 안정감을 줌</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -4360,7 +5349,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4368,12 +5357,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[항산화] 동화약품 배러크런치C 레몬맛 30정 10일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4383,23 +5372,35 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678604&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260825/GVr6GsoojIJO6UtcBMHG601678604_00_02GVr6GsoojIJO6UtcBMHG.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>123</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+        <v>7076</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 저렴한 가격에 부담 없이 꾸준히 복용하기 좋음</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>눈떨림 완화에 도움 — 눈떨림 증상이 있을 때 복용하기 유용함</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>편리한 섭취 — 복용 방식이 알맞고 챙겨 먹기 편함</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -4407,7 +5408,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4415,7 +5416,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>대웅제약 밀크씨슬 6정 6일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4425,27 +5426,35 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000280&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/1DUhwiP05cMCEONDxu7B600000280_00_011DUhwiP05cMCEONDxu7B.png</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>7557</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+        <v>335</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>소량 포장의 편리함 — 6일분 소량 포장으로 여행용이나 단기 섭취에 적합함</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 가격이 저렴하여 간 건강 관리에 부담이 없음</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -4454,7 +5463,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4462,12 +5471,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
+          <t>홀베리 유기농 레몬생강즙 10포</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4477,31 +5486,47 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000135&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923424&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/2ijoJLmHVT94XXIOZnda600000135_00_002ijoJLmHVT94XXIOZnda.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260904/TyBV46Gp3x0VYWqJvrvs965923424_00_00TyBV46Gp3x0VYWqJvrvs.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3762</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>612</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>소량 구매의 편의성 — 대량 구매 부담 없이 다이소에서 필요할 때 소량으로 살 수 있음</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>음료 활용 및 감기 기운 완화 — 물이나 탄산수에 타 마시기 좋고 감기 기운에 도움이 됨</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>알싸하고 매운 생강 맛 — 생생강 특유의 매운맛이 강해 기호에 따라 호불호가 갈림</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>자주 발생하는 품절 — 인기가 많아 다이소몰에서 자주 품절됨</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4509,39 +5534,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>[신혜선 PICK] 동국제약 프라임도스 비타민D3 4000IU 60정 60일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911095&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260414/Rr7eEkWvVmX4lCcRcfuW601618636_00_00Rr7eEkWvVmX4lCcRcfuW.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260814/OCdRZHWMgR1UGDUjFQp4610911095_00_01OCdRZHWMgR1UGDUjFQp4.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3740</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>저렴한 가격과 2개월 분량 — 5,000원에 2달 동안 먹을 수 있어 가성비가 매우 뛰어남</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>비타민K 복합 영양 성분 — 비타민D뿐만 아니라 비타민K가 함께 들어있어 만족스러움</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>상대적으로 낮은 함량 — 가격이 저렴한 만큼 성분 함량이 다소 낮게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -4656,52 +5693,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>혈행</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
     </row>
@@ -4713,24 +5750,24 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>자연관</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>종근당건강</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>판티오</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>CJ웰케어</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
@@ -4738,12 +5775,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -4753,12 +5790,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>동국제약</t>
         </is>
       </c>
     </row>
@@ -4770,52 +5807,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] [인교진 PICK] 스트레스 케어 올인원 15포 15일분</t>
+          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CJ 카무트 곡물과채콤부 화사 효소 10포 10일분</t>
+          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>대웅제약 콘드로이친 30정 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[항산화] 동화약품 배러크런치C 레몬맛 30정 10일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>대웅제약 밀크씨슬 6정 6일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
+          <t>홀베리 유기농 레몬생강즙 10포</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>[신혜선 PICK] 동국제약 프라임도스 비타민D3 4000IU 60정 60일분</t>
         </is>
       </c>
     </row>
@@ -4850,7 +5887,7 @@
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.8</v>
@@ -4863,69 +5900,135 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>904</v>
+        <v>7563</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>904</v>
+        <v>6868</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>124</v>
+        <v>1188</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1304</v>
+        <v>1888</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2970</v>
+        <v>1310</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>231</v>
+        <v>1561</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>123</v>
+        <v>7076</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>7557</v>
+        <v>335</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>3762</v>
+        <v>612</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>3740</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 합리적인 가격으로 부담 없이 구매 가능함
+피로 감소 체감 — 섭취 후 확실히 피로감이 줄어드는 느낌을 받음</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>저렴한 가격과 접근성 — 착한 가격에 부담 없이 구매하여 섭취할 수 있음
+입문용으로 적합 — 오메가3를 처음 접하는 입문자에게 적합함</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>상큼한 레몬 맛과 가성비 — 가격이 저렴하고 상큼하여 부담 없이 먹기 좋음
+공복 섭취의 간편함 — 아침 공복에 마시기 편리한 포장 구조임
+신속한 배송 — 배송이 빠르게 처리되어 받아볼 수 있음</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>작은 알약 크기와 목넘김 — 알약 크기가 작아 섭취 시 목넘김이 수월함
+편리한 케이스 포장 — 가위 없이 쉽게 뜯어지도록 설계된 케이스가 편리함
+높은 가성비 — 가격 대비 만족스러운 품질을 제공함</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>저렴한 가격과 가성비 — 가격이 매우 싸서 부담 없이 시도해보기 좋음
+빠른 배송 서비스 — 주문 후 배송이 빠름</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>우수한 가성비 — 타 다이어트 보조제 대비 가격이 매우 저렴함
+식후 마음의 안정 — 식사 후 복용 시 심리적으로 안정감을 줌</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 저렴한 가격에 부담 없이 꾸준히 복용하기 좋음
+눈떨림 완화에 도움 — 눈떨림 증상이 있을 때 복용하기 유용함
+편리한 섭취 — 복용 방식이 알맞고 챙겨 먹기 편함</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>소량 포장의 편리함 — 6일분 소량 포장으로 여행용이나 단기 섭취에 적합함
+뛰어난 가성비 — 가격이 저렴하여 간 건강 관리에 부담이 없음</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>소량 구매의 편의성 — 대량 구매 부담 없이 다이소에서 필요할 때 소량으로 살 수 있음
+음료 활용 및 감기 기운 완화 — 물이나 탄산수에 타 마시기 좋고 감기 기운에 도움이 됨</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>저렴한 가격과 2개월 분량 — 5,000원에 2달 동안 먹을 수 있어 가성비가 매우 뛰어남
+비타민K 복합 영양 성분 — 비타민D뿐만 아니라 비타민K가 함께 들어있어 만족스러움</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>미미한 효능 체감 — 단기 섭취 시 명확한 효과를 체감하기 어려움</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>알싸하고 매운 생강 맛 — 생생강 특유의 매운맛이 강해 기호에 따라 호불호가 갈림
+자주 발생하는 품절 — 인기가 많아 다이소몰에서 자주 품절됨</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>상대적으로 낮은 함량 — 가격이 저렴한 만큼 성분 함량이 다소 낮게 느껴질 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -4935,7 +6038,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -4960,27 +6063,27 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -5068,7 +6171,1042 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>이미지</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>상품URL</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>이미지URL</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>리뷰평점</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>리뷰건수</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>긍정1</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>긍정2</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>긍정3</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>부정1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>부정2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>부정3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>락토핏 맘스 60포 (2개월분)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>락토핏</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>19,900원</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000173821&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017382116ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>35,800원</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30,400원</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492948ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>락토핏 베베 60포 (2개월분)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>락토핏</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>17,500원</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000173816&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017381615ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>138</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[베러PICK] 온리추얼 비타민C 글로우업 트리플 7포+1포 (8일분)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>온리추얼</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000263899&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026389913ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>맛있는 레몬라임 맛 젤리 — 상큼한 레몬라임 맛 젤리스틱으로 맛이 뛰어남</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>풍부한 이중 영양 성분 — 비타민C와 글루타치온, 히알루론산을 한 번에 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>간편한 스틱 포장 — 하루 한 포씩 간편하게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>15,900원</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000261662&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026166204ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>27</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>1위</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2위</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>3위</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>4위</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>5위</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>6위</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>7위</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>8위</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>9위</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>10위</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="100" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>썸네일</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>락토핏</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>락토핏</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>온리추얼</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>락토핏 맘스 60포 (2개월분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>락토핏 베베 60포 (2개월분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[베러PICK] 온리추얼 비타민C 글로우업 트리플 7포+1포 (8일분)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>평점</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>리뷰수</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>긍정리뷰</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>맛있는 레몬라임 맛 젤리 — 상큼한 레몬라임 맛 젤리스틱으로 맛이 뛰어남
+풍부한 이중 영양 성분 — 비타민C와 글루타치온, 히알루론산을 한 번에 챙길 수 있음
+간편한 스틱 포장 — 하루 한 포씩 간편하게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>부정리뷰</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>19,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>35,800원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>30,400원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>17,500원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>15,900원</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A11"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5097,6 +7235,11 @@
           <t>다이소몰</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5105,10 +7248,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>33.3</v>
+        <v>35</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
@@ -5116,6 +7259,9 @@
       <c r="E2" t="n">
         <v>4</v>
       </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5124,16 +7270,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>17.5</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -5143,10 +7292,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
@@ -5154,37 +7303,43 @@
       <c r="E4" t="n">
         <v>1</v>
       </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -5192,43 +7347,140 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
